--- a/interview_forms/020_education_platform_interview_question_form--interview_forms.xlsx
+++ b/interview_forms/020_education_platform_interview_question_form--interview_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -757,8 +757,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -786,12 +786,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'teacher',_'value':_'teacher'}</t>
+          <t>teacher</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Teacher', 'value': 'teacher'}</t>
+          <t>Teacher</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'instructor',_'value':_'instructor'}</t>
+          <t>instructor</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Instructor', 'value': 'instructor'}</t>
+          <t>Instructor</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'administrator',_'value':_'administrator'}</t>
+          <t>administrator</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Administrator', 'value': 'administrator'}</t>
+          <t>Administrator</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'high_school',_'value':_'high_school'}</t>
+          <t>high_school</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'High School', 'value': 'high_school'}</t>
+          <t>High School</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_"bachelor's",_'value':_'bachelors'}</t>
+          <t>bachelor's</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': "Bachelor's", 'value': 'bachelors'}</t>
+          <t>Bachelor's</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_"master's",_'value':_'masters'}</t>
+          <t>master's</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': "Master's", 'value': 'masters'}</t>
+          <t>Master's</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'ph.d.',_'value':_'phd'}</t>
+          <t>ph.d.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Ph.D.', 'value': 'phd'}</t>
+          <t>Ph.D.</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'morning',_'value':_'morning'}</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Morning', 'value': 'morning'}</t>
+          <t>Morning</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'afternoon',_'value':_'afternoon'}</t>
+          <t>afternoon</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Afternoon', 'value': 'afternoon'}</t>
+          <t>Afternoon</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'evening',_'value':_'evening'}</t>
+          <t>evening</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Evening', 'value': 'evening'}</t>
+          <t>Evening</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'morning',_'value':_'morning'}</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'morning', 'value': 'morning'}</t>
+          <t>morning</t>
         </is>
       </c>
     </row>
@@ -973,12 +973,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'afternoon',_'value':_'afternoon'}</t>
+          <t>afternoon</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'afternoon', 'value': 'afternoon'}</t>
+          <t>afternoon</t>
         </is>
       </c>
     </row>
@@ -990,12 +990,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'evening',_'value':_'evening'}</t>
+          <t>evening</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'evening', 'value': 'evening'}</t>
+          <t>evening</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'monday',_'value':_'monday'}</t>
+          <t>monday</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Monday', 'value': 'monday'}</t>
+          <t>Monday</t>
         </is>
       </c>
     </row>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'tuesday',_'value':_'tuesday'}</t>
+          <t>tuesday</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Tuesday', 'value': 'tuesday'}</t>
+          <t>Tuesday</t>
         </is>
       </c>
     </row>
@@ -1041,12 +1041,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'wednesday',_'value':_'wednesday'}</t>
+          <t>wednesday</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Wednesday', 'value': 'wednesday'}</t>
+          <t>Wednesday</t>
         </is>
       </c>
     </row>
@@ -1058,12 +1058,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'thursday',_'value':_'thursday'}</t>
+          <t>thursday</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Thursday', 'value': 'thursday'}</t>
+          <t>Thursday</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'friday',_'value':_'friday'}</t>
+          <t>friday</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Friday', 'value': 'friday'}</t>
+          <t>Friday</t>
         </is>
       </c>
     </row>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'saturday',_'value':_'saturday'}</t>
+          <t>saturday</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'Saturday', 'value': 'saturday'}</t>
+          <t>Saturday</t>
         </is>
       </c>
     </row>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'sunday',_'value':_'sunday'}</t>
+          <t>sunday</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': 'Sunday', 'value': 'sunday'}</t>
+          <t>Sunday</t>
         </is>
       </c>
     </row>
@@ -1126,12 +1126,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'pacific',_'value':_'pacific'}</t>
+          <t>pacific</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Pacific', 'value': 'pacific'}</t>
+          <t>Pacific</t>
         </is>
       </c>
     </row>
@@ -1143,12 +1143,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'eastern',_'value':_'eastern'}</t>
+          <t>eastern</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Eastern', 'value': 'eastern'}</t>
+          <t>Eastern</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'central',_'value':_'central'}</t>
+          <t>central</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Central', 'value': 'central'}</t>
+          <t>Central</t>
         </is>
       </c>
     </row>
@@ -1177,12 +1177,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'mountain',_'value':_'mountain'}</t>
+          <t>mountain</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Mountain', 'value': 'mountain'}</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'gmt-05',_'value':_'gmt_05'}</t>
+          <t>gmt-05</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'GMT-05', 'value': 'gmt_05'}</t>
+          <t>GMT-05</t>
         </is>
       </c>
     </row>
@@ -1211,12 +1211,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'gmt-08',_'value':_'gmt_08'}</t>
+          <t>gmt-08</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'GMT-08', 'value': 'gmt_08'}</t>
+          <t>GMT-08</t>
         </is>
       </c>
     </row>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_7,_'label':_'gmt-11',_'value':_'gmt_11'}</t>
+          <t>gmt-11</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 7, 'label': 'GMT-11', 'value': 'gmt_11'}</t>
+          <t>GMT-11</t>
         </is>
       </c>
     </row>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_8,_'label':_'gmt-14',_'value':_'gmt_14'}</t>
+          <t>gmt-14</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 8, 'label': 'GMT-14', 'value': 'gmt_14'}</t>
+          <t>GMT-14</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1262,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_9,_'label':_'gmt-16',_'value':_'gmt_16'}</t>
+          <t>gmt-16</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 9, 'label': 'GMT-16', 'value': 'gmt_16'}</t>
+          <t>GMT-16</t>
         </is>
       </c>
     </row>
@@ -1279,12 +1279,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_10,_'label':_'gmt-18',_'value':_'gmt_18'}</t>
+          <t>gmt-18</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 10, 'label': 'GMT-18', 'value': 'gmt_18'}</t>
+          <t>GMT-18</t>
         </is>
       </c>
     </row>
